--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F940"/>
+  <dimension ref="A1:F941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22992,6 +22992,30 @@
         <v>216.49</v>
       </c>
       <c r="F940" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>222.74</v>
+      </c>
+      <c r="C941" t="n">
+        <v>225.24</v>
+      </c>
+      <c r="D941" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="E941" t="n">
+        <v>215.87</v>
+      </c>
+      <c r="F941" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23008,7 +23032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1068"/>
+  <dimension ref="A1:B1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33691,6 +33715,16 @@
       </c>
       <c r="B1068" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -33853,28 +33887,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16173676203486</v>
+        <v>0.1627110647441109</v>
       </c>
       <c r="J2" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K2" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08340248852385657</v>
+        <v>0.08440558620730332</v>
       </c>
       <c r="M2" t="n">
-        <v>3.360615275734174</v>
+        <v>3.361969257311029</v>
       </c>
       <c r="N2" t="n">
-        <v>16.00073880319339</v>
+        <v>16.00564618898862</v>
       </c>
       <c r="O2" t="n">
-        <v>4.000092349333124</v>
+        <v>4.00070571137001</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9186681226591</v>
+        <v>213.9087048456118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33925,28 +33959,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1174622436436816</v>
+        <v>0.1180383951566044</v>
       </c>
       <c r="J3" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K3" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0648757703076086</v>
+        <v>0.06557708175995991</v>
       </c>
       <c r="M3" t="n">
-        <v>2.902688757751998</v>
+        <v>2.902551521895024</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06894549864921</v>
+        <v>11.06483857553006</v>
       </c>
       <c r="O3" t="n">
-        <v>3.327002479507524</v>
+        <v>3.326385211536701</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4483842937665</v>
+        <v>219.4424925343677</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33997,28 +34031,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1118430941685747</v>
+        <v>0.111842589080984</v>
       </c>
       <c r="J4" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K4" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0566282891056028</v>
+        <v>0.05675666733313911</v>
       </c>
       <c r="M4" t="n">
-        <v>2.953382898530985</v>
+        <v>2.950243510139983</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59820117834964</v>
+        <v>11.58586267235128</v>
       </c>
       <c r="O4" t="n">
-        <v>3.405613186835764</v>
+        <v>3.403801209288122</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6628852802229</v>
+        <v>221.6628904452784</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34069,28 +34103,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01917609869726757</v>
+        <v>0.0188961498737778</v>
       </c>
       <c r="J5" t="n">
+        <v>940</v>
+      </c>
+      <c r="K5" t="n">
         <v>939</v>
       </c>
-      <c r="K5" t="n">
-        <v>938</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.002145019649817614</v>
+        <v>0.002087603161882723</v>
       </c>
       <c r="M5" t="n">
-        <v>2.539895207123552</v>
+        <v>2.538760272892617</v>
       </c>
       <c r="N5" t="n">
-        <v>9.489014507771536</v>
+        <v>9.480710714495968</v>
       </c>
       <c r="O5" t="n">
-        <v>3.080424403839759</v>
+        <v>3.079076276173744</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6664057799562</v>
+        <v>216.6692757393418</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34128,7 +34162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F940"/>
+  <dimension ref="A1:F941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64207,6 +64241,38 @@
         </is>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>-41.026860212218374,173.02003710248104</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>-41.0262126569825,173.01961843441367</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>-41.02557847548523,173.0191748354511</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>-41.02500512133204,173.01884977184207</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F941"/>
+  <dimension ref="A1:F943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23016,6 +23016,54 @@
         <v>215.87</v>
       </c>
       <c r="F941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>222.56</v>
+      </c>
+      <c r="C942" t="n">
+        <v>224.97</v>
+      </c>
+      <c r="D942" t="n">
+        <v>224.04</v>
+      </c>
+      <c r="E942" t="n">
+        <v>215.64</v>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>222.25</v>
+      </c>
+      <c r="C943" t="n">
+        <v>224.18</v>
+      </c>
+      <c r="D943" t="n">
+        <v>223.05</v>
+      </c>
+      <c r="E943" t="n">
+        <v>215.05</v>
+      </c>
+      <c r="F943" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23032,7 +23080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1069"/>
+  <dimension ref="A1:B1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33725,6 +33773,26 @@
       </c>
       <c r="B1069" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -33887,28 +33955,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1627110647441109</v>
+        <v>0.1645006450610495</v>
       </c>
       <c r="J2" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K2" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08440558620730332</v>
+        <v>0.08630801338972005</v>
       </c>
       <c r="M2" t="n">
-        <v>3.361969257311029</v>
+        <v>3.363865506384585</v>
       </c>
       <c r="N2" t="n">
-        <v>16.00564618898862</v>
+        <v>16.00880446497234</v>
       </c>
       <c r="O2" t="n">
-        <v>4.00070571137001</v>
+        <v>4.001100406759662</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9087048456118</v>
+        <v>213.8903788836123</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33959,28 +34027,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1180383951566044</v>
+        <v>0.1188960900292135</v>
       </c>
       <c r="J3" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K3" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06557708175995991</v>
+        <v>0.06671941263408998</v>
       </c>
       <c r="M3" t="n">
-        <v>2.902551521895024</v>
+        <v>2.900760151456474</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06483857553006</v>
+        <v>11.05020048267723</v>
       </c>
       <c r="O3" t="n">
-        <v>3.326385211536701</v>
+        <v>3.324184183025547</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4424925343677</v>
+        <v>219.4337100828945</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34031,28 +34099,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.111842589080984</v>
+        <v>0.1113840570809762</v>
       </c>
       <c r="J4" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K4" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05675666733313911</v>
+        <v>0.05656115140083473</v>
       </c>
       <c r="M4" t="n">
-        <v>2.950243510139983</v>
+        <v>2.946255318635911</v>
       </c>
       <c r="N4" t="n">
-        <v>11.58586267235128</v>
+        <v>11.56422606449489</v>
       </c>
       <c r="O4" t="n">
-        <v>3.403801209288122</v>
+        <v>3.400621423283529</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6628904452784</v>
+        <v>221.6675871011338</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34103,28 +34171,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0188961498737778</v>
+        <v>0.01811666443570704</v>
       </c>
       <c r="J5" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K5" t="n">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002087603161882723</v>
+        <v>0.001927046055500758</v>
       </c>
       <c r="M5" t="n">
-        <v>2.538760272892617</v>
+        <v>2.537713999324782</v>
       </c>
       <c r="N5" t="n">
-        <v>9.480710714495968</v>
+        <v>9.467745617143041</v>
       </c>
       <c r="O5" t="n">
-        <v>3.079076276173744</v>
+        <v>3.076970200886424</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6692757393418</v>
+        <v>216.6772787208623</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34162,7 +34230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F941"/>
+  <dimension ref="A1:F943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64273,6 +64341,70 @@
         </is>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>-41.026860970434946,173.020035209852</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>-41.026213794297185,173.01961559549065</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>-41.02558081571526,173.01916880046133</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>-41.02500512129714,173.0188470360183</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>-41.02686227625233,173.0200319503241</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>-41.02621712199527,173.01960728901167</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>-41.025584880324544,173.01915831863593</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>-41.02500512120732,173.0188400180355</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F943"/>
+  <dimension ref="A1:F946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23064,6 +23064,78 @@
         <v>215.05</v>
       </c>
       <c r="F943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>222.11</v>
+      </c>
+      <c r="C944" t="n">
+        <v>223.54</v>
+      </c>
+      <c r="D944" t="n">
+        <v>222.24</v>
+      </c>
+      <c r="E944" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>221.88</v>
+      </c>
+      <c r="C945" t="n">
+        <v>223.36</v>
+      </c>
+      <c r="D945" t="n">
+        <v>222.33</v>
+      </c>
+      <c r="E945" t="n">
+        <v>214.42</v>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>221.61</v>
+      </c>
+      <c r="C946" t="n">
+        <v>223.21</v>
+      </c>
+      <c r="D946" t="n">
+        <v>222.17</v>
+      </c>
+      <c r="E946" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="F946" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23080,7 +23152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1071"/>
+  <dimension ref="A1:B1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33793,6 +33865,36 @@
       </c>
       <c r="B1071" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -33955,28 +34057,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1645006450610495</v>
+        <v>0.1668042243332659</v>
       </c>
       <c r="J2" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K2" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08630801338972005</v>
+        <v>0.08890256878008718</v>
       </c>
       <c r="M2" t="n">
-        <v>3.363865506384585</v>
+        <v>3.364858192871095</v>
       </c>
       <c r="N2" t="n">
-        <v>16.00880446497234</v>
+        <v>15.99917955642802</v>
       </c>
       <c r="O2" t="n">
-        <v>4.001100406759662</v>
+        <v>3.999897443238767</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8903788836123</v>
+        <v>213.8667211099338</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34027,28 +34129,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1188960900292135</v>
+        <v>0.1193936591393769</v>
       </c>
       <c r="J3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06671941263408998</v>
+        <v>0.06768481500140222</v>
       </c>
       <c r="M3" t="n">
-        <v>2.900760151456474</v>
+        <v>2.894065176869608</v>
       </c>
       <c r="N3" t="n">
-        <v>11.05020048267723</v>
+        <v>11.01709632866988</v>
       </c>
       <c r="O3" t="n">
-        <v>3.324184183025547</v>
+        <v>3.319201158211096</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4337100828945</v>
+        <v>219.4286007434477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34099,28 +34201,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1113840570809762</v>
+        <v>0.1098700197857386</v>
       </c>
       <c r="J4" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K4" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05656115140083473</v>
+        <v>0.0554151853181335</v>
       </c>
       <c r="M4" t="n">
-        <v>2.946255318635911</v>
+        <v>2.944392720032743</v>
       </c>
       <c r="N4" t="n">
-        <v>11.56422606449489</v>
+        <v>11.54525913364671</v>
       </c>
       <c r="O4" t="n">
-        <v>3.400621423283529</v>
+        <v>3.397831534029712</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6675871011338</v>
+        <v>221.683137479389</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34171,28 +34273,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01811666443570704</v>
+        <v>0.01635787924336481</v>
       </c>
       <c r="J5" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K5" t="n">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001927046055500758</v>
+        <v>0.001579030712168805</v>
       </c>
       <c r="M5" t="n">
-        <v>2.537713999324782</v>
+        <v>2.539419919490992</v>
       </c>
       <c r="N5" t="n">
-        <v>9.467745617143041</v>
+        <v>9.461467622377032</v>
       </c>
       <c r="O5" t="n">
-        <v>3.076970200886424</v>
+        <v>3.075949873189912</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6772787208623</v>
+        <v>216.6953877640837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34230,7 +34332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F943"/>
+  <dimension ref="A1:F946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64405,6 +64507,102 @@
         </is>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>-41.02686286597628,173.02003047827918</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>-41.026219817851505,173.01960055971168</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>-41.02558820591325,173.01914974259603</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>-41.02500512110786,173.01883228635953</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>-41.026863834808445,173.0200280599196</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>-41.026220576061,173.01959866709595</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>-41.025587836403425,173.0191506954894</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>-41.02500512111093,173.01883252425725</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>-41.02686497213308,173.02002522097573</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>-41.02622120790223,173.01959708991612</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>-41.025588493309776,173.01914900145675</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>-41.02500512110786,173.01883228635953</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F946"/>
+  <dimension ref="A1:F950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23136,6 +23136,102 @@
         <v>214.4</v>
       </c>
       <c r="F946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>220.82</v>
+      </c>
+      <c r="C947" t="n">
+        <v>222.41</v>
+      </c>
+      <c r="D947" t="n">
+        <v>221.31</v>
+      </c>
+      <c r="E947" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>219.78</v>
+      </c>
+      <c r="C948" t="n">
+        <v>221.93</v>
+      </c>
+      <c r="D948" t="n">
+        <v>220.53</v>
+      </c>
+      <c r="E948" t="n">
+        <v>213.31</v>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="C949" t="n">
+        <v>220.98</v>
+      </c>
+      <c r="D949" t="n">
+        <v>220.01</v>
+      </c>
+      <c r="E949" t="n">
+        <v>212.42</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>218.21</v>
+      </c>
+      <c r="C950" t="n">
+        <v>220.85</v>
+      </c>
+      <c r="D950" t="n">
+        <v>220.15</v>
+      </c>
+      <c r="E950" t="n">
+        <v>212.93</v>
+      </c>
+      <c r="F950" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23152,7 +23248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1074"/>
+  <dimension ref="A1:B1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33895,6 +33991,46 @@
       </c>
       <c r="B1074" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
@@ -34057,28 +34193,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1668042243332659</v>
+        <v>0.1677308880970485</v>
       </c>
       <c r="J2" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K2" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08890256878008718</v>
+        <v>0.09054663497346738</v>
       </c>
       <c r="M2" t="n">
-        <v>3.364858192871095</v>
+        <v>3.355574224317012</v>
       </c>
       <c r="N2" t="n">
-        <v>15.99917955642802</v>
+        <v>15.94095520968284</v>
       </c>
       <c r="O2" t="n">
-        <v>3.999897443238767</v>
+        <v>3.992612579462581</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8667211099338</v>
+        <v>213.857178524909</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34129,28 +34265,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1193936591393769</v>
+        <v>0.118494894357783</v>
       </c>
       <c r="J3" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K3" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06768481500140222</v>
+        <v>0.06730229686265199</v>
       </c>
       <c r="M3" t="n">
-        <v>2.894065176869608</v>
+        <v>2.88622690626783</v>
       </c>
       <c r="N3" t="n">
-        <v>11.01709632866988</v>
+        <v>10.97717093490057</v>
       </c>
       <c r="O3" t="n">
-        <v>3.319201158211096</v>
+        <v>3.313181391789555</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4286007434477</v>
+        <v>219.4378707788829</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34201,28 +34337,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1098700197857386</v>
+        <v>0.1064047179178304</v>
       </c>
       <c r="J4" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K4" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0554151853181335</v>
+        <v>0.0523257020984309</v>
       </c>
       <c r="M4" t="n">
-        <v>2.944392720032743</v>
+        <v>2.949017458328594</v>
       </c>
       <c r="N4" t="n">
-        <v>11.54525913364671</v>
+        <v>11.56767122646979</v>
       </c>
       <c r="O4" t="n">
-        <v>3.397831534029712</v>
+        <v>3.401127934446128</v>
       </c>
       <c r="P4" t="n">
-        <v>221.683137479389</v>
+        <v>221.7188607033832</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34273,28 +34409,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01635787924336481</v>
+        <v>0.01292509712388279</v>
       </c>
       <c r="J5" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K5" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001579030712168805</v>
+        <v>0.0009887101287269218</v>
       </c>
       <c r="M5" t="n">
-        <v>2.539419919490992</v>
+        <v>2.547725896213318</v>
       </c>
       <c r="N5" t="n">
-        <v>9.461467622377032</v>
+        <v>9.490781257991165</v>
       </c>
       <c r="O5" t="n">
-        <v>3.075949873189912</v>
+        <v>3.080711161078098</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6953877640837</v>
+        <v>216.7308628359413</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34332,7 +34468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F946"/>
+  <dimension ref="A1:F950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64603,6 +64739,134 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>-41.026868299860325,173.02001691443556</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>-41.02622457772171,173.01958867828995</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>-41.025592024180995,173.0191398960306</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>-41.02500512099247,173.01882336519495</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>-41.026872680664894,173.0200059792422</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>-41.02622659961311,173.01958363131385</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>-41.02559522659843,173.01913163762</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>-41.02500512093993,173.0188193209337</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>-41.02687680872979,173.01999567492405</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>-41.02623060127254,173.01957364250606</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>-41.02559736154305,173.0191261320125</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>-41.025005120801715,173.01880873448505</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>-41.02687929399291,173.0199894713033</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>-41.026231148867964,173.01957227561647</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>-41.0255967867503,173.0191276142915</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>-41.025005120881026,173.01881480087698</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F950"/>
+  <dimension ref="A1:F954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23232,6 +23232,102 @@
         <v>212.93</v>
       </c>
       <c r="F950" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>217.38</v>
+      </c>
+      <c r="C951" t="n">
+        <v>219.96</v>
+      </c>
+      <c r="D951" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="E951" t="n">
+        <v>212.76</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>217.27</v>
+      </c>
+      <c r="C952" t="n">
+        <v>220.14</v>
+      </c>
+      <c r="D952" t="n">
+        <v>220.17</v>
+      </c>
+      <c r="E952" t="n">
+        <v>213.32</v>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>217.83</v>
+      </c>
+      <c r="C953" t="n">
+        <v>220.24</v>
+      </c>
+      <c r="D953" t="n">
+        <v>220.47</v>
+      </c>
+      <c r="E953" t="n">
+        <v>213.88</v>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>217.31</v>
+      </c>
+      <c r="C954" t="n">
+        <v>219.89</v>
+      </c>
+      <c r="D954" t="n">
+        <v>220.56</v>
+      </c>
+      <c r="E954" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="F954" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23248,7 +23344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1078"/>
+  <dimension ref="A1:B1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34031,6 +34127,46 @@
       </c>
       <c r="B1078" t="n">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -34193,28 +34329,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1677308880970485</v>
+        <v>0.1669864841972143</v>
       </c>
       <c r="J2" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K2" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09054663497346738</v>
+        <v>0.09058753303093225</v>
       </c>
       <c r="M2" t="n">
-        <v>3.355574224317012</v>
+        <v>3.3451189369777</v>
       </c>
       <c r="N2" t="n">
-        <v>15.94095520968284</v>
+        <v>15.87751769322676</v>
       </c>
       <c r="O2" t="n">
-        <v>3.992612579462581</v>
+        <v>3.984660298347497</v>
       </c>
       <c r="P2" t="n">
-        <v>213.857178524909</v>
+        <v>213.8648816114835</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34265,28 +34401,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.118494894357783</v>
+        <v>0.1163580924883305</v>
       </c>
       <c r="J3" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K3" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06730229686265199</v>
+        <v>0.0654898030754979</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88622690626783</v>
+        <v>2.884368643281765</v>
       </c>
       <c r="N3" t="n">
-        <v>10.97717093490057</v>
+        <v>10.95799350311426</v>
       </c>
       <c r="O3" t="n">
-        <v>3.313181391789555</v>
+        <v>3.310286015303551</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4378707788829</v>
+        <v>219.4599830441771</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34337,28 +34473,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1064047179178304</v>
+        <v>0.1027965119835129</v>
       </c>
       <c r="J4" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K4" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0523257020984309</v>
+        <v>0.04914647052935817</v>
       </c>
       <c r="M4" t="n">
-        <v>2.949017458328594</v>
+        <v>2.954363133267973</v>
       </c>
       <c r="N4" t="n">
-        <v>11.56767122646979</v>
+        <v>11.59592876016188</v>
       </c>
       <c r="O4" t="n">
-        <v>3.401127934446128</v>
+        <v>3.405279542146558</v>
       </c>
       <c r="P4" t="n">
-        <v>221.7188607033832</v>
+        <v>221.7561972148921</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34409,28 +34545,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01292509712388279</v>
+        <v>0.009885253396021535</v>
       </c>
       <c r="J5" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K5" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009887101287269218</v>
+        <v>0.0005807872971750339</v>
       </c>
       <c r="M5" t="n">
-        <v>2.547725896213318</v>
+        <v>2.553986587814923</v>
       </c>
       <c r="N5" t="n">
-        <v>9.490781257991165</v>
+        <v>9.505850723245862</v>
       </c>
       <c r="O5" t="n">
-        <v>3.080711161078098</v>
+        <v>3.083155968037599</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7308628359413</v>
+        <v>216.7623947149766</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34468,7 +34604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F950"/>
+  <dimension ref="A1:F954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64867,6 +65003,134 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>-41.02688279020994,173.01998074417506</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>-41.02623489779009,173.0195629176795</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>-41.02559805950566,173.0191243321023</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>-41.02500512085464,173.01881277874634</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>-41.02688325356396,173.01997958756763</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>-41.02623413958117,173.01956481029606</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>-41.02559670463706,173.01912782604563</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>-41.02500512094147,173.01881943988252</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>-41.02688089467067,173.01998547575073</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>-41.02623371835399,173.01956586174967</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>-41.02559547293821,173.01913100235762</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>-41.02500512102793,173.01882610101876</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>-41.026883085071596,173.01998000815215</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>-41.0262351926491,173.01956218166194</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>-41.02559510342853,173.0191319552512</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>-41.02500512103101,173.01882633891648</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F954"/>
+  <dimension ref="A1:F960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23328,6 +23328,150 @@
         <v>213.9</v>
       </c>
       <c r="F954" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="C955" t="n">
+        <v>219.43</v>
+      </c>
+      <c r="D955" t="n">
+        <v>220.58</v>
+      </c>
+      <c r="E955" t="n">
+        <v>213.95</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="C956" t="n">
+        <v>219.43</v>
+      </c>
+      <c r="D956" t="n">
+        <v>220.79</v>
+      </c>
+      <c r="E956" t="n">
+        <v>214.37</v>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="C957" t="n">
+        <v>219.26</v>
+      </c>
+      <c r="D957" t="n">
+        <v>220.64</v>
+      </c>
+      <c r="E957" t="n">
+        <v>215.05</v>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="C958" t="n">
+        <v>219.49</v>
+      </c>
+      <c r="D958" t="n">
+        <v>220.99</v>
+      </c>
+      <c r="E958" t="n">
+        <v>215.38</v>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="C959" t="n">
+        <v>218.34</v>
+      </c>
+      <c r="D959" t="n">
+        <v>219.91</v>
+      </c>
+      <c r="E959" t="n">
+        <v>215.38</v>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>214.83</v>
+      </c>
+      <c r="C960" t="n">
+        <v>218.66</v>
+      </c>
+      <c r="D960" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="E960" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="F960" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23344,7 +23488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1082"/>
+  <dimension ref="A1:B1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34167,6 +34311,66 @@
       </c>
       <c r="B1082" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -34329,28 +34533,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1669864841972143</v>
+        <v>0.1630473143348074</v>
       </c>
       <c r="J2" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K2" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09058753303093225</v>
+        <v>0.08753912629441674</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3451189369777</v>
+        <v>3.343245111842353</v>
       </c>
       <c r="N2" t="n">
-        <v>15.87751769322676</v>
+        <v>15.84341440854583</v>
       </c>
       <c r="O2" t="n">
-        <v>3.984660298347497</v>
+        <v>3.980378676526372</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8648816114835</v>
+        <v>213.9057889102385</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34401,28 +34605,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1163580924883305</v>
+        <v>0.1120433207653876</v>
       </c>
       <c r="J3" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K3" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0654898030754979</v>
+        <v>0.06144004782942181</v>
       </c>
       <c r="M3" t="n">
-        <v>2.884368643281765</v>
+        <v>2.886776043792552</v>
       </c>
       <c r="N3" t="n">
-        <v>10.95799350311426</v>
+        <v>10.96457638988152</v>
       </c>
       <c r="O3" t="n">
-        <v>3.310286015303551</v>
+        <v>3.311280173872565</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4599830441771</v>
+        <v>219.5047859918264</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34473,28 +34677,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1027965119835129</v>
+        <v>0.09788295851575826</v>
       </c>
       <c r="J4" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K4" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04914647052935817</v>
+        <v>0.04502073421420194</v>
       </c>
       <c r="M4" t="n">
-        <v>2.954363133267973</v>
+        <v>2.95984179616645</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59592876016188</v>
+        <v>11.61996937346099</v>
       </c>
       <c r="O4" t="n">
-        <v>3.405279542146558</v>
+        <v>3.408807617549133</v>
       </c>
       <c r="P4" t="n">
-        <v>221.7561972148921</v>
+        <v>221.8072146724679</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34545,28 +34749,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009885253396021535</v>
+        <v>0.00742157767755392</v>
       </c>
       <c r="J5" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K5" t="n">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005807872971750339</v>
+        <v>0.0003312130201335028</v>
       </c>
       <c r="M5" t="n">
-        <v>2.553986587814923</v>
+        <v>2.551780639642932</v>
       </c>
       <c r="N5" t="n">
-        <v>9.505850723245862</v>
+        <v>9.473590227787451</v>
       </c>
       <c r="O5" t="n">
-        <v>3.083155968037599</v>
+        <v>3.077919789043803</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7623947149766</v>
+        <v>216.7880277326155</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34604,7 +34808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F954"/>
+  <dimension ref="A1:F960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65131,6 +65335,198 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>-41.026886623410995,173.01997117587675</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>-41.026237130293914,173.01955734497494</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>-41.025595021315276,173.01913216700532</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>-41.02500512103872,173.01882693366076</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>-41.02688872956509,173.0199659185695</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>-41.026237130293914,173.01955734497494</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>-41.02559415912601,173.01913439042363</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>-41.025005121103256,173.01883192951294</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>-41.026894584672156,173.0199513032536</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>-41.02623784637999,173.0195555575036</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>-41.02559477497549,173.01913280226773</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>-41.02500512120732,173.0188400180355</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>-41.026894584672156,173.0199513032536</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>-41.02623687755765,173.0195579758472</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>-41.02559333799334,173.01913650796482</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>-41.02500512125761,173.0188439433479</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>-41.026894584672156,173.0199513032536</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>-41.02624172166886,173.01954588412858</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>-41.0255977721093,173.0191250732418</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>-41.02500512125761,173.0188439433479</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>-41.026893531595505,173.01995393190774</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>-41.02624037374238,173.0195492487809</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>-41.02559567822136,173.0191304729723</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>-41.02500512137444,173.0188531024102</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F960"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23472,6 +23472,126 @@
         <v>216.15</v>
       </c>
       <c r="F960" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>214.46</v>
+      </c>
+      <c r="C961" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="D961" t="n">
+        <v>221.13</v>
+      </c>
+      <c r="E961" t="n">
+        <v>217.1</v>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="C962" t="n">
+        <v>219.12</v>
+      </c>
+      <c r="D962" t="n">
+        <v>221.52</v>
+      </c>
+      <c r="E962" t="n">
+        <v>217.61</v>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>214.15</v>
+      </c>
+      <c r="C963" t="n">
+        <v>219.39</v>
+      </c>
+      <c r="D963" t="n">
+        <v>222.01</v>
+      </c>
+      <c r="E963" t="n">
+        <v>219.14</v>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="C964" t="n">
+        <v>219.64</v>
+      </c>
+      <c r="D964" t="n">
+        <v>222.59</v>
+      </c>
+      <c r="E964" t="n">
+        <v>219.88</v>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>214.88</v>
+      </c>
+      <c r="C965" t="n">
+        <v>219.55</v>
+      </c>
+      <c r="D965" t="n">
+        <v>223.1</v>
+      </c>
+      <c r="E965" t="n">
+        <v>219.88</v>
+      </c>
+      <c r="F965" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23488,7 +23608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1088"/>
+  <dimension ref="A1:B1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34371,6 +34491,56 @@
       </c>
       <c r="B1088" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -34533,28 +34703,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1630473143348074</v>
+        <v>0.1591838235805541</v>
       </c>
       <c r="J2" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K2" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08753912629441674</v>
+        <v>0.08433727963828808</v>
       </c>
       <c r="M2" t="n">
-        <v>3.343245111842353</v>
+        <v>3.34462398091604</v>
       </c>
       <c r="N2" t="n">
-        <v>15.84341440854583</v>
+        <v>15.8339216898731</v>
       </c>
       <c r="O2" t="n">
-        <v>3.980378676526372</v>
+        <v>3.979186058715162</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9057889102385</v>
+        <v>213.9460452634817</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34605,28 +34775,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1120433207653876</v>
+        <v>0.1087358400778827</v>
       </c>
       <c r="J3" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K3" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06144004782942181</v>
+        <v>0.05845210866056205</v>
       </c>
       <c r="M3" t="n">
-        <v>2.886776043792552</v>
+        <v>2.887315238431265</v>
       </c>
       <c r="N3" t="n">
-        <v>10.96457638988152</v>
+        <v>10.96130706584326</v>
       </c>
       <c r="O3" t="n">
-        <v>3.311280173872565</v>
+        <v>3.31078647240248</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5047859918264</v>
+        <v>219.539247129847</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34677,28 +34847,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09788295851575826</v>
+        <v>0.0954593123026917</v>
       </c>
       <c r="J4" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K4" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04502073421420194</v>
+        <v>0.0432889624694347</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95984179616645</v>
+        <v>2.95622731760139</v>
       </c>
       <c r="N4" t="n">
-        <v>11.61996937346099</v>
+        <v>11.59083954663056</v>
       </c>
       <c r="O4" t="n">
-        <v>3.408807617549133</v>
+        <v>3.404532206725406</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8072146724679</v>
+        <v>221.8324610260754</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34749,28 +34919,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00742157767755392</v>
+        <v>0.009207424432189906</v>
       </c>
       <c r="J5" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K5" t="n">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003312130201335028</v>
+        <v>0.0005145353811902842</v>
       </c>
       <c r="M5" t="n">
-        <v>2.551780639642932</v>
+        <v>2.546368618784161</v>
       </c>
       <c r="N5" t="n">
-        <v>9.473590227787451</v>
+        <v>9.446732931234616</v>
       </c>
       <c r="O5" t="n">
-        <v>3.077919789043803</v>
+        <v>3.073553795077388</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7880277326155</v>
+        <v>216.7693604630573</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34808,7 +34978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F960"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65527,6 +65697,166 @@
         </is>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>-41.026895090148955,173.0199500414996</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>-41.026239994638054,173.01955019508932</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>-41.025592763200436,173.01913799024362</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>-41.02500512151759,173.01886440255197</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>-41.02689492165671,173.01995046208427</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>-41.026238436097906,173.01955408546834</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>-41.025591161991564,173.0191421194487</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>-41.02500512159396,173.0188704689439</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>-41.02689639596392,173.01994678196832</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>-41.026237298784764,173.01955692439347</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>-41.0255891502161,173.01914730742402</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>-41.025005121821195,173.01888866811964</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>-41.02689450042604,173.01995151354595</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>-41.026236245716966,173.01955955302776</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>-41.02558676893055,173.0191534482924</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>-41.025005121930086,173.01889747033533</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>-41.02689332098015,173.01995445763856</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>-41.02623662482137,173.01955860671941</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>-41.02558467504129,173.0191588480211</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>-41.025005121930086,173.01889747033533</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0576/nzd0576.xlsx
+++ b/data/nzd0576/nzd0576.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F965"/>
+  <dimension ref="A1:F968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23592,6 +23592,78 @@
         <v>219.88</v>
       </c>
       <c r="F965" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>215.17</v>
+      </c>
+      <c r="C966" t="n">
+        <v>219.92</v>
+      </c>
+      <c r="D966" t="n">
+        <v>223.66</v>
+      </c>
+      <c r="E966" t="n">
+        <v>220.46</v>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>215.02</v>
+      </c>
+      <c r="C967" t="n">
+        <v>219.95</v>
+      </c>
+      <c r="D967" t="n">
+        <v>223.89</v>
+      </c>
+      <c r="E967" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>215.17</v>
+      </c>
+      <c r="C968" t="n">
+        <v>220.15</v>
+      </c>
+      <c r="D968" t="n">
+        <v>224.11</v>
+      </c>
+      <c r="E968" t="n">
+        <v>220.35</v>
+      </c>
+      <c r="F968" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23608,7 +23680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1093"/>
+  <dimension ref="A1:B1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34541,6 +34613,36 @@
       </c>
       <c r="B1093" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34703,28 +34805,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1591838235805541</v>
+        <v>0.157275655017699</v>
       </c>
       <c r="J2" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K2" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08433727963828808</v>
+        <v>0.08288488006275552</v>
       </c>
       <c r="M2" t="n">
-        <v>3.34462398091604</v>
+        <v>3.343481345304683</v>
       </c>
       <c r="N2" t="n">
-        <v>15.8339216898731</v>
+        <v>15.81456361038629</v>
       </c>
       <c r="O2" t="n">
-        <v>3.979186058715162</v>
+        <v>3.976752897828363</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9460452634817</v>
+        <v>213.9659923731099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34775,28 +34877,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1087358400778827</v>
+        <v>0.1072268847943263</v>
       </c>
       <c r="J3" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K3" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05845210866056205</v>
+        <v>0.05722032171868996</v>
       </c>
       <c r="M3" t="n">
-        <v>2.887315238431265</v>
+        <v>2.8854339523656</v>
       </c>
       <c r="N3" t="n">
-        <v>10.96130706584326</v>
+        <v>10.9459374544261</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31078647240248</v>
+        <v>3.308464516120145</v>
       </c>
       <c r="P3" t="n">
-        <v>219.539247129847</v>
+        <v>219.5550208178995</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34847,28 +34949,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0954593123026917</v>
+        <v>0.09514237532815099</v>
       </c>
       <c r="J4" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K4" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0432889624694347</v>
+        <v>0.04330204056817077</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95622731760139</v>
+        <v>2.948575328966539</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59083954663056</v>
+        <v>11.55580306325579</v>
       </c>
       <c r="O4" t="n">
-        <v>3.404532206725406</v>
+        <v>3.399382747390442</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8324610260754</v>
+        <v>221.8357736854326</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34919,28 +35021,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009207424432189906</v>
+        <v>0.01128964797269274</v>
       </c>
       <c r="J5" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K5" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005145353811902842</v>
+        <v>0.0007759397494259135</v>
       </c>
       <c r="M5" t="n">
-        <v>2.546368618784161</v>
+        <v>2.547629802824421</v>
       </c>
       <c r="N5" t="n">
-        <v>9.446732931234616</v>
+        <v>9.452658742002281</v>
       </c>
       <c r="O5" t="n">
-        <v>3.073553795077388</v>
+        <v>3.074517643794272</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7693604630573</v>
+        <v>216.7475408365118</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34978,7 +35080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F965"/>
+  <dimension ref="A1:F968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65857,6 +65959,102 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>-41.026892099411114,173.01995750687723</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>-41.02623506628096,173.01956249709806</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>-41.025582375868424,173.01916477713456</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>-41.02500512201495,173.0189043693693</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>-41.02689273125717,173.0199559296848</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>-41.026234939912804,173.01956281253413</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>-41.02558143156521,173.01916721230606</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>-41.02500512200619,173.01890365567613</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>-41.026892099411114,173.01995750687723</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>-41.02623409745846,173.01956491544144</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>-41.0255805283186,173.01916954160046</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>-41.02500512199887,173.01890306093182</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
